--- a/data/masterdata/Materials.xlsx
+++ b/data/masterdata/Materials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beotalk-my.sharepoint.com/personal/tora_bang-olufsen_dk/Documents/Dokumenter/GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27897C1A-5DC4-4153-90E0-AC52DF38B918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{27897C1A-5DC4-4153-90E0-AC52DF38B918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3E45B51-61C2-4874-8153-6AC43A313C92}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A8B817EE-B692-4E35-9DD7-8FB9369AB787}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Material ID</t>
   </si>
@@ -47,13 +47,25 @@
     <t>Material Name</t>
   </si>
   <si>
-    <t>Family</t>
-  </si>
-  <si>
     <t>Density</t>
   </si>
   <si>
-    <t>Material Cost EUR/kg</t>
+    <t>Material Group</t>
+  </si>
+  <si>
+    <t>Default Price EUR kg</t>
+  </si>
+  <si>
+    <t>AL_6082</t>
+  </si>
+  <si>
+    <t>Aluminium EN AW-6082</t>
+  </si>
+  <si>
+    <t>Aluminium</t>
+  </si>
+  <si>
+    <t>3.50</t>
   </si>
 </sst>
 </file>
@@ -95,10 +107,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,10 +449,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0E898A-B1E8-4C3D-BF2B-E23091F7DDB8}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="39.26953125" customWidth="1"/>
+    <col min="1" max="5" width="26.90625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -448,13 +464,30 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2700</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Materials.xlsx
+++ b/data/masterdata/Materials.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beotalk-my.sharepoint.com/personal/tora_bang-olufsen_dk/Documents/Dokumenter/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{27897C1A-5DC4-4153-90E0-AC52DF38B918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3E45B51-61C2-4874-8153-6AC43A313C92}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6817D55F-3E80-4A05-82F7-E192CE3D7B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A8B817EE-B692-4E35-9DD7-8FB9369AB787}"/>
   </bookViews>
@@ -41,21 +41,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>Material ID</t>
-  </si>
-  <si>
-    <t>Material Name</t>
-  </si>
-  <si>
     <t>Density</t>
   </si>
   <si>
-    <t>Material Group</t>
-  </si>
-  <si>
-    <t>Default Price EUR kg</t>
-  </si>
-  <si>
     <t>AL_6082</t>
   </si>
   <si>
@@ -66,6 +54,18 @@
   </si>
   <si>
     <t>3.50</t>
+  </si>
+  <si>
+    <t>Material_ID</t>
+  </si>
+  <si>
+    <t>Material_Name</t>
+  </si>
+  <si>
+    <t>Material_Group</t>
+  </si>
+  <si>
+    <t>Default_Price_EUR_kg</t>
   </si>
 </sst>
 </file>
@@ -458,36 +458,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2">
         <v>2700</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Materials.xlsx
+++ b/data/masterdata/Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6817D55F-3E80-4A05-82F7-E192CE3D7B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F61999F-7C59-47F2-9220-F5893166C4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A8B817EE-B692-4E35-9DD7-8FB9369AB787}"/>
+    <workbookView xWindow="-55080" yWindow="2730" windowWidth="21600" windowHeight="12525" xr2:uid="{A8B817EE-B692-4E35-9DD7-8FB9369AB787}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,17 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
   <si>
     <t>Density</t>
   </si>
   <si>
-    <t>AL_6082</t>
-  </si>
-  <si>
-    <t>Aluminium EN AW-6082</t>
-  </si>
-  <si>
     <t>Aluminium</t>
   </si>
   <si>
@@ -66,6 +60,180 @@
   </si>
   <si>
     <t>Default_Price_EUR_kg</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>Polypropylene</t>
+  </si>
+  <si>
+    <t>Polymer</t>
+  </si>
+  <si>
+    <t>1.80</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
+    <t>2.50</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Polycarbonate</t>
+  </si>
+  <si>
+    <t>4.50</t>
+  </si>
+  <si>
+    <t>PC_ABS</t>
+  </si>
+  <si>
+    <t>PC-ABS</t>
+  </si>
+  <si>
+    <t>4.20</t>
+  </si>
+  <si>
+    <t>PA6</t>
+  </si>
+  <si>
+    <t>Polyamide 6</t>
+  </si>
+  <si>
+    <t>3.20</t>
+  </si>
+  <si>
+    <t>PA66</t>
+  </si>
+  <si>
+    <t>Polyamide 66</t>
+  </si>
+  <si>
+    <t>3.80</t>
+  </si>
+  <si>
+    <t>PA6_GF30</t>
+  </si>
+  <si>
+    <t>PA6 GF30</t>
+  </si>
+  <si>
+    <t>PA66_GF30</t>
+  </si>
+  <si>
+    <t>PA66 GF30</t>
+  </si>
+  <si>
+    <t>4.80</t>
+  </si>
+  <si>
+    <t>PBT</t>
+  </si>
+  <si>
+    <t>PBT_GF30</t>
+  </si>
+  <si>
+    <t>PBT GF30</t>
+  </si>
+  <si>
+    <t>POM</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>PMMA</t>
+  </si>
+  <si>
+    <t>Acrylic (PMMA)</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>2.60</t>
+  </si>
+  <si>
+    <t>ASA</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>Elastomer</t>
+  </si>
+  <si>
+    <t>TPU</t>
+  </si>
+  <si>
+    <t>5.50</t>
+  </si>
+  <si>
+    <t>PPS</t>
+  </si>
+  <si>
+    <t>High Performance Polymer</t>
+  </si>
+  <si>
+    <t>12.00</t>
+  </si>
+  <si>
+    <t>PEEK</t>
+  </si>
+  <si>
+    <t>60.00</t>
+  </si>
+  <si>
+    <t>LCP</t>
+  </si>
+  <si>
+    <t>18.00</t>
+  </si>
+  <si>
+    <t>AL6082</t>
+  </si>
+  <si>
+    <t>EN AW-6082 T6</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>https://www.theworldmaterial.com/6082-aluminum/</t>
+  </si>
+  <si>
+    <t>European structural alloy; suitable for premium machined and anodised parts.</t>
+  </si>
+  <si>
+    <t>AL6061</t>
+  </si>
+  <si>
+    <t>AA 6061-T6</t>
+  </si>
+  <si>
+    <t>https://www.theworldmaterial.com/al-6061-t6-aluminum-alloy/</t>
+  </si>
+  <si>
+    <t>General-purpose wrought alloy with good machinability and corrosion resistance.</t>
+  </si>
+  <si>
+    <t>ADC12</t>
+  </si>
+  <si>
+    <t>https://www.ycumetal.com/density-of-aluminum-alloys/</t>
+  </si>
+  <si>
+    <t>High-volume die-casting alloy; verify cosmetic surface and porosity requirements.</t>
+  </si>
+  <si>
+    <t>A380</t>
+  </si>
+  <si>
+    <t>Common HPDC alloy for housings and structural components.</t>
   </si>
 </sst>
 </file>
@@ -107,13 +275,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,45 +626,471 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0E898A-B1E8-4C3D-BF2B-E23091F7DDB8}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="26.90625" style="2" customWidth="1"/>
     <col min="6" max="7" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2710</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2700</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2750</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2740</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>900</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1040</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1150</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1140</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1140</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1360</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1360</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1310</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2">
-        <v>2700</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1540</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1420</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1180</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1080</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1070</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="3">
+        <v>950</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1350</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1320</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1450</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="K27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="K28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="K29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="K30" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
